--- a/output/pdf_financials_xlsx/ROCK.xlsx
+++ b/output/pdf_financials_xlsx/ROCK.xlsx
@@ -7814,25 +7814,25 @@
         <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-1.363122</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.7438709999999999</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.240082</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-3.74927</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.209547</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.157118</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-3.311592</v>
       </c>
     </row>
     <row r="119">
@@ -26958,7 +26958,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -31032,7 +31036,11 @@
           <t>Recovery of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ROCK.xlsx
+++ b/output/pdf_financials_xlsx/ROCK.xlsx
@@ -1065,40 +1065,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.101052</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.015468</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.01461</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.020439</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.020449</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.014393</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.133858</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.06819600000000001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.06648800000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.043116</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.048561</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.036781</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1110,13 +1110,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.1528</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.022932</v>
       </c>
     </row>
     <row r="13">
@@ -2060,40 +2060,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.029127</v>
+        <v>-6.130179</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.895226</v>
+        <v>-0.910694</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.448055</v>
+        <v>-0.462665</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.6173729999999999</v>
+        <v>-0.637812</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.4545</v>
+        <v>-0.474949</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.929612</v>
+        <v>-1.944005</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.448859</v>
+        <v>-3.582717</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.977604</v>
+        <v>-2.0458</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.063771</v>
+        <v>-3.130259</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.511658</v>
+        <v>-3.554774</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-5.420721</v>
+        <v>-5.469282</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.372077</v>
+        <v>2.335296</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>12.142799</v>
@@ -2105,13 +2105,13 @@
         <v>-7.354906</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-4.250601</v>
+        <v>-4.250676</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>1.489826</v>
+        <v>1.337026</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>4.476676</v>
+        <v>4.453744</v>
       </c>
     </row>
     <row r="28">
@@ -2182,40 +2182,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.029127</v>
+        <v>-6.130179</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.895226</v>
+        <v>-0.910694</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.448055</v>
+        <v>-0.462665</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.6173729999999999</v>
+        <v>-0.637812</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.4545</v>
+        <v>-0.474949</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.929612</v>
+        <v>-1.944005</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.448859</v>
+        <v>-3.582717</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.977604</v>
+        <v>-2.0458</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.063771</v>
+        <v>-3.130259</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.511658</v>
+        <v>-3.554774</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-5.420721</v>
+        <v>-5.469282</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.372077</v>
+        <v>2.335296</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>12.142799</v>
@@ -2227,13 +2227,13 @@
         <v>-7.354906</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.250601</v>
+        <v>-4.250676</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>1.489826</v>
+        <v>1.337026</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4.476676</v>
+        <v>4.453744</v>
       </c>
     </row>
     <row r="30">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-960.7320002516969</v>
+        <v>-972.5278302906279</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-2154.148568794433</v>
+        <v>-2173.446298496668</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>7783.17091577255</v>
+        <v>7662.486465203268</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-72386.28315946348</v>
@@ -2306,7 +2306,7 @@
         <v>-29419624</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-5667468</v>
+        <v>-5667568</v>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
@@ -2477,19 +2477,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.049719</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.685415</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.685415</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.760788</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.227964</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.570562</v>
@@ -2510,25 +2510,25 @@
         <v>0.8274049999999999</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.224544</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.713549</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.434258</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.061074</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.127904</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.130368</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>4.741705</v>
       </c>
     </row>
     <row r="35">
@@ -2599,19 +2599,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.049719</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.685415</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.685415</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.760788</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.227964</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.570562</v>
@@ -2632,25 +2632,25 @@
         <v>5.117919</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>4.13838</v>
+        <v>4.362924</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>17.885855</v>
+        <v>19.599404</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>20.677456</v>
+        <v>21.111714</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>9.63504</v>
+        <v>9.696114</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>6.630645</v>
+        <v>6.758549</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>8.260089000000001</v>
+        <v>8.390457</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>9.561712999999999</v>
+        <v>14.303418</v>
       </c>
     </row>
     <row r="37">
@@ -3331,19 +3331,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.068616</v>
+        <v>0.018897</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.701749</v>
+        <v>0.016334</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.701749</v>
+        <v>0.016334</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.772122</v>
+        <v>0.011334</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.239333</v>
+        <v>0.011369</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.036947</v>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -44548,7 +44548,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E345" s="5" t="n">
@@ -51846,7 +51846,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -58062,7 +58062,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">

--- a/output/pdf_financials_xlsx/ROCK.xlsx
+++ b/output/pdf_financials_xlsx/ROCK.xlsx
@@ -1391,16 +1391,16 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.70278</v>
+        <v>-0.70278</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.88</v>
+        <v>-0.88</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.023505</v>
+        <v>-0.023505</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0.416472</v>
@@ -1409,7 +1409,7 @@
         <v>-0.409946</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.309743</v>
+        <v>-0.155467</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0.069822</v>
@@ -2365,7 +2365,7 @@
         <v>3.376042047636628</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>39.96998473428231</v>
+        <v>20.0618371252447</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0.9493255250305035</v>
@@ -7320,22 +7320,22 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.001029</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.00376</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.00194</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.003974</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.004093</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.004215</v>
       </c>
       <c r="Q110" s="3" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001475</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -7616,40 +7616,40 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.067514</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>1.222282</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>3.279125</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.514485</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>1.867144</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>3.155152</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>1.668343</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>1.687178</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>1.153733</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>1.293174</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>6.401332</v>
       </c>
     </row>
     <row r="116">
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001475</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.663079</v>
+        <v>-0.664554</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.364304</v>
@@ -26766,7 +26766,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -27160,7 +27164,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -28774,7 +28782,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -29484,7 +29496,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -35500,7 +35516,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -36450,7 +36470,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -39080,7 +39104,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -41720,7 +41748,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E317" s="5" t="n">
         <v>-0.001475</v>
       </c>
@@ -44844,7 +44876,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -46798,7 +46834,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -48698,7 +48738,11 @@
           <t>Current income tax recovery 10</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -54386,7 +54430,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -55448,7 +55496,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -57540,7 +57592,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
